--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,6 +133,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -157,8 +161,12 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>深创100ETF</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -179,6 +187,10 @@
   <si>
     <t>成交均量</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>利润</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -601,7 +613,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -763,6 +775,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -772,7 +787,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -933,6 +948,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -976,7 +994,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1138,6 +1156,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1147,7 +1168,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1309,6 +1330,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13918241.906652076</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14227459.764016345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1351,7 +1375,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1513,6 +1537,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1522,7 +1549,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1684,6 +1711,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4556907.088924652</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4866124.9462889209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1705,11 +1735,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="313126272"/>
-        <c:axId val="313128832"/>
+        <c:axId val="523589120"/>
+        <c:axId val="523596160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="313126272"/>
+        <c:axId val="523589120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1752,14 +1782,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="313128832"/>
+        <c:crossAx val="523596160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="313128832"/>
+        <c:axId val="523596160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1810,7 +1840,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="313126272"/>
+        <c:crossAx val="523589120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2001,7 +2031,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2163,6 +2193,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-73556.079313855051</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-244188.52262430632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2177,8 +2210,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="475052288"/>
-        <c:axId val="475050752"/>
+        <c:axId val="732805376"/>
+        <c:axId val="732803840"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2203,7 +2236,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2365,6 +2398,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2374,7 +2410,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2536,6 +2572,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2552,11 +2591,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475010560"/>
-        <c:axId val="475012096"/>
+        <c:axId val="732606464"/>
+        <c:axId val="732608768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475010560"/>
+        <c:axId val="732606464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2599,14 +2638,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475012096"/>
+        <c:crossAx val="732608768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475012096"/>
+        <c:axId val="732608768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2657,12 +2696,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475010560"/>
+        <c:crossAx val="732606464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="475050752"/>
+        <c:axId val="732803840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2699,12 +2738,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475052288"/>
+        <c:crossAx val="732805376"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="475052288"/>
+        <c:axId val="732805376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2713,7 +2752,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="475050752"/>
+        <c:crossAx val="732803840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2875,7 +2914,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3037,6 +3076,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3051,8 +3093,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="426957824"/>
-        <c:axId val="426955904"/>
+        <c:axId val="532622336"/>
+        <c:axId val="532620800"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3077,7 +3119,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3239,6 +3281,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3248,7 +3293,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3410,6 +3455,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3426,11 +3474,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426935808"/>
-        <c:axId val="426937344"/>
+        <c:axId val="532615936"/>
+        <c:axId val="532618624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426935808"/>
+        <c:axId val="532615936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3473,14 +3521,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426937344"/>
+        <c:crossAx val="532618624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426937344"/>
+        <c:axId val="532618624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3531,12 +3579,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426935808"/>
+        <c:crossAx val="532615936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="426955904"/>
+        <c:axId val="532620800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3573,12 +3621,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426957824"/>
+        <c:crossAx val="532622336"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="426957824"/>
+        <c:axId val="532622336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3587,7 +3635,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426955904"/>
+        <c:crossAx val="532620800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3766,7 +3814,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3928,6 +3976,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3937,7 +3988,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4098,6 +4149,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4141,7 +4195,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4303,6 +4357,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4312,7 +4369,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4474,6 +4531,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>14963307.508744044</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15294247.764746865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4516,7 +4576,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4678,6 +4738,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4687,7 +4750,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4849,6 +4912,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4955533.9692211729</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5286474.2252239939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4870,11 +4936,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="560845184"/>
-        <c:axId val="560846720"/>
+        <c:axId val="532911616"/>
+        <c:axId val="532913536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="560845184"/>
+        <c:axId val="532911616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4917,14 +4983,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560846720"/>
+        <c:crossAx val="532913536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="560846720"/>
+        <c:axId val="532913536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4975,7 +5041,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560845184"/>
+        <c:crossAx val="532911616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5166,7 +5232,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5328,6 +5394,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-76300.054631715335</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-131316.53344699508</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5342,8 +5411,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="590915456"/>
-        <c:axId val="590913536"/>
+        <c:axId val="685244800"/>
+        <c:axId val="682609280"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5368,7 +5437,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5530,6 +5599,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5539,7 +5611,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5701,6 +5773,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5717,11 +5792,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="590893440"/>
-        <c:axId val="590894976"/>
+        <c:axId val="680527360"/>
+        <c:axId val="682607360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="590893440"/>
+        <c:axId val="680527360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5764,14 +5839,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590894976"/>
+        <c:crossAx val="682607360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="590894976"/>
+        <c:axId val="682607360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5822,12 +5897,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590893440"/>
+        <c:crossAx val="680527360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="590913536"/>
+        <c:axId val="682609280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5864,12 +5939,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590915456"/>
+        <c:crossAx val="685244800"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="590915456"/>
+        <c:axId val="685244800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5878,7 +5953,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="590913536"/>
+        <c:crossAx val="682609280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6057,7 +6132,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6219,6 +6294,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6228,7 +6306,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6389,6 +6467,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6432,7 +6513,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6594,6 +6675,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6603,7 +6687,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6765,6 +6849,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>14844133.861885205</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15173385.354710398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6807,7 +6894,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6969,6 +7056,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6978,7 +7068,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7140,6 +7230,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4881348.482635295</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5210599.9754604883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7161,11 +7254,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="591191424"/>
-        <c:axId val="591221888"/>
+        <c:axId val="704481152"/>
+        <c:axId val="704482688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="591191424"/>
+        <c:axId val="704481152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7208,14 +7301,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591221888"/>
+        <c:crossAx val="704482688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="591221888"/>
+        <c:axId val="704482688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7266,7 +7359,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591191424"/>
+        <c:crossAx val="704481152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7457,7 +7550,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7619,6 +7712,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7633,8 +7729,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="591415936"/>
-        <c:axId val="591413632"/>
+        <c:axId val="721494784"/>
+        <c:axId val="704501632"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7659,7 +7755,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7821,6 +7917,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7830,7 +7929,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7992,6 +8091,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8008,11 +8110,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="591385344"/>
-        <c:axId val="591387264"/>
+        <c:axId val="704497536"/>
+        <c:axId val="704499712"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="591385344"/>
+        <c:axId val="704497536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8055,14 +8157,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591387264"/>
+        <c:crossAx val="704499712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="591387264"/>
+        <c:axId val="704499712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8113,12 +8215,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591385344"/>
+        <c:crossAx val="704497536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="591413632"/>
+        <c:axId val="704501632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8155,12 +8257,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591415936"/>
+        <c:crossAx val="721494784"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="591415936"/>
+        <c:axId val="721494784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8169,7 +8271,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="591413632"/>
+        <c:crossAx val="704501632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8348,7 +8450,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8510,6 +8612,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8519,7 +8624,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8680,6 +8785,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8723,7 +8831,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8885,6 +8993,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8894,7 +9005,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9056,6 +9167,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>132401493.54502271</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>135374422.21281305</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9098,7 +9212,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9260,6 +9374,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9269,7 +9386,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9431,6 +9548,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>44961540.882420003</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>47934469.550210342</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9452,11 +9572,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="592430592"/>
-        <c:axId val="592432512"/>
+        <c:axId val="721609472"/>
+        <c:axId val="721611392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="592430592"/>
+        <c:axId val="721609472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9499,14 +9619,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="592432512"/>
+        <c:crossAx val="721611392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="592432512"/>
+        <c:axId val="721611392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9557,7 +9677,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="592430592"/>
+        <c:crossAx val="721609472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9748,7 +9868,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9910,6 +10030,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>123871776.79126592</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>123330440.59734799</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9924,8 +10047,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="593945728"/>
-        <c:axId val="593763328"/>
+        <c:axId val="722283520"/>
+        <c:axId val="722281984"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9950,7 +10073,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10112,6 +10235,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10121,7 +10247,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10283,6 +10409,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10299,11 +10428,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="593754368"/>
-        <c:axId val="593761024"/>
+        <c:axId val="722126720"/>
+        <c:axId val="722280448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="593754368"/>
+        <c:axId val="722126720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10346,14 +10475,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593761024"/>
+        <c:crossAx val="722280448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="593761024"/>
+        <c:axId val="722280448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10404,12 +10533,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593754368"/>
+        <c:crossAx val="722126720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="593763328"/>
+        <c:axId val="722281984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10446,12 +10575,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593945728"/>
+        <c:crossAx val="722283520"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="593945728"/>
+        <c:axId val="722283520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10460,7 +10589,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="593763328"/>
+        <c:crossAx val="722281984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10639,7 +10768,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10801,6 +10930,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10810,7 +10942,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10971,6 +11103,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11014,7 +11149,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11176,6 +11311,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11185,7 +11323,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11347,6 +11485,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>136510246.47001591</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>139607183.83490777</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11389,7 +11530,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11551,6 +11692,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11560,7 +11704,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11722,6 +11866,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>52929250.134395897</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>56026187.499287754</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11743,11 +11890,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="473421696"/>
-        <c:axId val="473423232"/>
+        <c:axId val="731821952"/>
+        <c:axId val="731829760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="473421696"/>
+        <c:axId val="731821952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11790,14 +11937,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473423232"/>
+        <c:crossAx val="731829760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="473423232"/>
+        <c:axId val="731829760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11848,7 +11995,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473421696"/>
+        <c:crossAx val="731821952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12562,7 +12709,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -12693,28 +12840,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -14975,6 +15122,44 @@
       </c>
       <c r="L56" s="14">
         <v>518829.06704185653</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="15">
+        <v>12781203.118754858</v>
+      </c>
+      <c r="H57" s="15">
+        <v>13599200.252435327</v>
+      </c>
+      <c r="I57" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J57" s="15">
+        <v>14227459.764016345</v>
+      </c>
+      <c r="K57" s="15">
+        <v>4866124.9462889209</v>
+      </c>
+      <c r="L57" s="14">
+        <v>628259.51158101915</v>
       </c>
     </row>
   </sheetData>
@@ -14993,7 +15178,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15028,13 +15213,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -15064,10 +15249,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15088,7 +15273,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -15168,28 +15353,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -18697,6 +18882,71 @@
         <v>128.53526904457513</v>
       </c>
       <c r="U56" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-131316.53344699508</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-123417.79337621325</v>
+      </c>
+      <c r="G57" s="15">
+        <v>13665731.59556484</v>
+      </c>
+      <c r="H57" s="15">
+        <v>14540338.561040219</v>
+      </c>
+      <c r="I57" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J57" s="15">
+        <v>15294247.764746865</v>
+      </c>
+      <c r="K57" s="15">
+        <v>5286474.2252239939</v>
+      </c>
+      <c r="L57" s="14">
+        <v>753909.20370664692</v>
+      </c>
+      <c r="M57" s="23">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="N57" s="23">
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="O57" s="23">
+        <v>1.0713333288828533</v>
+      </c>
+      <c r="P57" s="23">
+        <v>0.88464285929997755</v>
+      </c>
+      <c r="Q57" s="23">
+        <v>0.18669046958287572</v>
+      </c>
+      <c r="R57" s="23">
+        <v>0.10844557342075166</v>
+      </c>
+      <c r="S57" s="9">
+        <v>1.6266836013112747E-3</v>
+      </c>
+      <c r="T57" s="9">
+        <v>114.76753649719217</v>
+      </c>
+      <c r="U57" s="11">
         <v>1.2</v>
       </c>
     </row>
@@ -18716,7 +18966,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -18751,13 +19001,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -18790,7 +19040,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -18857,28 +19107,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -21441,6 +21691,50 @@
         <v>-25.623704638394841</v>
       </c>
       <c r="N56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="15">
+        <v>13615936.237991611</v>
+      </c>
+      <c r="H57" s="15">
+        <v>14487356.300059929</v>
+      </c>
+      <c r="I57" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J57" s="15">
+        <v>15173385.354710398</v>
+      </c>
+      <c r="K57" s="15">
+        <v>5210599.9754604883</v>
+      </c>
+      <c r="L57" s="14">
+        <v>686029.05465046817</v>
+      </c>
+      <c r="M57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="N57" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21460,7 +21754,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -21501,7 +21795,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -21534,7 +21828,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -21601,28 +21895,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -24185,6 +24479,50 @@
         <v>-25.623704638394841</v>
       </c>
       <c r="N56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-575981.71600752324</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-541336.19391793292</v>
+      </c>
+      <c r="G57" s="15">
+        <v>123330440.59734799</v>
+      </c>
+      <c r="H57" s="15">
+        <v>131223590.08936608</v>
+      </c>
+      <c r="I57" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J57" s="15">
+        <v>135374422.21281305</v>
+      </c>
+      <c r="K57" s="15">
+        <v>47934469.550210342</v>
+      </c>
+      <c r="L57" s="14">
+        <v>4150832.1234469572</v>
+      </c>
+      <c r="M57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="N57" s="9">
         <v>1</v>
       </c>
     </row>
@@ -24204,7 +24542,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24239,22 +24577,22 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -24275,7 +24613,7 @@
         <v>16</v>
       </c>
       <c r="M1" s="27" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N1" s="28" t="s">
         <v>18</v>
@@ -24284,7 +24622,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -24359,28 +24697,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -27261,6 +27599,56 @@
         <v>-25.623704638394841</v>
       </c>
       <c r="P56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="14">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="14">
+        <v>-244188.52262430632</v>
+      </c>
+      <c r="H57" s="15">
+        <v>-229500.48892551727</v>
+      </c>
+      <c r="I57" s="15">
+        <v>128809294.87697572</v>
+      </c>
+      <c r="J57" s="15">
+        <v>137053091.10036543</v>
+      </c>
+      <c r="K57" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L57" s="15">
+        <v>139607183.83490777</v>
+      </c>
+      <c r="M57" s="15">
+        <v>56026187.499287754</v>
+      </c>
+      <c r="N57" s="14">
+        <v>2554092.7345423289</v>
+      </c>
+      <c r="O57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="P57" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -165,10 +165,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>PE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -181,16 +177,24 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>标志</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>成交量</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>成交均量</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>利润</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -613,7 +617,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -778,6 +782,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -787,7 +794,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -951,6 +958,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -994,7 +1004,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1159,6 +1169,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1168,7 +1181,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1333,6 +1346,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>14227459.764016345</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14329709.596181171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1375,7 +1391,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1540,6 +1556,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1549,7 +1568,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1714,6 +1733,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>4866124.9462889209</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4968374.7784537468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1735,11 +1757,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523589120"/>
-        <c:axId val="523596160"/>
+        <c:axId val="90875008"/>
+        <c:axId val="90882048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523589120"/>
+        <c:axId val="90875008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1782,14 +1804,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523596160"/>
+        <c:crossAx val="90882048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523596160"/>
+        <c:axId val="90882048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1840,7 +1862,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523589120"/>
+        <c:crossAx val="90875008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2031,7 +2053,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2196,6 +2218,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-244188.52262430632</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-637497.67999171233</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2210,8 +2235,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="732805376"/>
-        <c:axId val="732803840"/>
+        <c:axId val="563940352"/>
+        <c:axId val="563938816"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2236,7 +2261,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2401,6 +2426,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2410,7 +2438,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2575,6 +2603,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2591,11 +2622,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="732606464"/>
-        <c:axId val="732608768"/>
+        <c:axId val="542664960"/>
+        <c:axId val="563937280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="732606464"/>
+        <c:axId val="542664960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2638,14 +2669,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="732608768"/>
+        <c:crossAx val="563937280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="732608768"/>
+        <c:axId val="563937280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2696,12 +2727,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="732606464"/>
+        <c:crossAx val="542664960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="732803840"/>
+        <c:axId val="563938816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2738,12 +2769,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="732805376"/>
+        <c:crossAx val="563940352"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="732805376"/>
+        <c:axId val="563940352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2752,7 +2783,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="732803840"/>
+        <c:crossAx val="563938816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2914,7 +2945,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3079,6 +3110,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3093,8 +3127,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="532622336"/>
-        <c:axId val="532620800"/>
+        <c:axId val="564147328"/>
+        <c:axId val="382270080"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3119,7 +3153,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3284,6 +3318,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3293,7 +3330,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3458,6 +3495,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3474,11 +3514,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="532615936"/>
-        <c:axId val="532618624"/>
+        <c:axId val="91220224"/>
+        <c:axId val="382268160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="532615936"/>
+        <c:axId val="91220224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3521,14 +3561,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532618624"/>
+        <c:crossAx val="382268160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="532618624"/>
+        <c:axId val="382268160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3579,12 +3619,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532615936"/>
+        <c:crossAx val="91220224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="532620800"/>
+        <c:axId val="382270080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3621,12 +3661,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532622336"/>
+        <c:crossAx val="564147328"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="532622336"/>
+        <c:axId val="564147328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3635,7 +3675,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="532620800"/>
+        <c:crossAx val="382270080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3814,7 +3854,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3979,6 +4019,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3988,7 +4031,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4152,6 +4195,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4195,7 +4241,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4360,6 +4406,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4369,7 +4418,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4534,6 +4583,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15294247.764746865</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15403573.839066558</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4576,7 +4628,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4741,6 +4793,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4750,7 +4805,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4915,6 +4970,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5286474.2252239939</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5395800.2995436862</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4936,11 +4994,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="532911616"/>
-        <c:axId val="532913536"/>
+        <c:axId val="624962176"/>
+        <c:axId val="648290304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="532911616"/>
+        <c:axId val="624962176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4983,14 +5041,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532913536"/>
+        <c:crossAx val="648290304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="532913536"/>
+        <c:axId val="648290304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5041,7 +5099,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532911616"/>
+        <c:crossAx val="624962176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5232,7 +5290,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5397,6 +5455,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-131316.53344699508</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5411,8 +5472,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="685244800"/>
-        <c:axId val="682609280"/>
+        <c:axId val="654992512"/>
+        <c:axId val="648334336"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5437,7 +5498,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5602,6 +5663,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5611,7 +5675,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5776,6 +5840,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5792,11 +5859,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="680527360"/>
-        <c:axId val="682607360"/>
+        <c:axId val="648310144"/>
+        <c:axId val="648332416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="680527360"/>
+        <c:axId val="648310144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5839,14 +5906,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="682607360"/>
+        <c:crossAx val="648332416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="682607360"/>
+        <c:axId val="648332416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5897,12 +5964,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="680527360"/>
+        <c:crossAx val="648310144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="682609280"/>
+        <c:axId val="648334336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5939,12 +6006,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="685244800"/>
+        <c:crossAx val="654992512"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="685244800"/>
+        <c:axId val="654992512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5953,7 +6020,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="682609280"/>
+        <c:crossAx val="648334336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6132,7 +6199,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6297,6 +6364,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6306,7 +6376,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6470,6 +6540,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6513,7 +6586,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6678,6 +6751,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6687,7 +6763,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6852,6 +6928,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15173385.354710398</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15282313.065362198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6894,7 +6973,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7059,6 +7138,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7068,7 +7150,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7233,6 +7315,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5210599.9754604883</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5319527.6861122884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7254,11 +7339,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="704481152"/>
-        <c:axId val="704482688"/>
+        <c:axId val="655176064"/>
+        <c:axId val="655178368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="704481152"/>
+        <c:axId val="655176064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7301,14 +7386,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704482688"/>
+        <c:crossAx val="655178368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="704482688"/>
+        <c:axId val="655178368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7359,7 +7444,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704481152"/>
+        <c:crossAx val="655176064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7550,7 +7635,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7715,6 +7800,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7729,8 +7817,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="721494784"/>
-        <c:axId val="704501632"/>
+        <c:axId val="656342400"/>
+        <c:axId val="656340480"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7755,7 +7843,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7920,6 +8008,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7929,7 +8020,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8094,6 +8185,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8110,11 +8204,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="704497536"/>
-        <c:axId val="704499712"/>
+        <c:axId val="656315904"/>
+        <c:axId val="656338944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="704497536"/>
+        <c:axId val="656315904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8157,14 +8251,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704499712"/>
+        <c:crossAx val="656338944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="704499712"/>
+        <c:axId val="656338944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8215,12 +8309,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704497536"/>
+        <c:crossAx val="656315904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="704501632"/>
+        <c:axId val="656340480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8257,12 +8351,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721494784"/>
+        <c:crossAx val="656342400"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="721494784"/>
+        <c:axId val="656342400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8271,7 +8365,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="704501632"/>
+        <c:crossAx val="656340480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8450,7 +8544,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8615,6 +8709,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8624,7 +8721,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8788,6 +8885,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8831,7 +8931,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8996,6 +9096,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9005,7 +9108,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9170,6 +9273,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>135374422.21281305</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>136361067.73708206</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9212,7 +9318,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9377,6 +9483,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9386,7 +9495,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9551,6 +9660,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>47934469.550210342</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>48921115.074479356</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9572,11 +9684,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="721609472"/>
-        <c:axId val="721611392"/>
+        <c:axId val="656405632"/>
+        <c:axId val="656560128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="721609472"/>
+        <c:axId val="656405632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9619,14 +9731,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721611392"/>
+        <c:crossAx val="656560128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="721611392"/>
+        <c:axId val="656560128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9677,7 +9789,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721609472"/>
+        <c:crossAx val="656405632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9868,7 +9980,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10033,6 +10145,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>123330440.59734799</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>122634814.91739957</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10047,8 +10162,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="722283520"/>
-        <c:axId val="722281984"/>
+        <c:axId val="659614336"/>
+        <c:axId val="659612416"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10073,7 +10188,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10238,6 +10353,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10247,7 +10365,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10412,6 +10530,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10428,11 +10549,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="722126720"/>
-        <c:axId val="722280448"/>
+        <c:axId val="657760640"/>
+        <c:axId val="657762944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="722126720"/>
+        <c:axId val="657760640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10475,14 +10596,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="722280448"/>
+        <c:crossAx val="657762944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="722280448"/>
+        <c:axId val="657762944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10533,12 +10654,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="722126720"/>
+        <c:crossAx val="657760640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="722281984"/>
+        <c:axId val="659612416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10575,12 +10696,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="722283520"/>
+        <c:crossAx val="659614336"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="722283520"/>
+        <c:axId val="659614336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10589,7 +10710,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="722281984"/>
+        <c:crossAx val="659612416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10768,7 +10889,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10933,6 +11054,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10942,7 +11066,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11106,6 +11230,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11149,7 +11276,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11314,6 +11441,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11323,7 +11453,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11488,6 +11618,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>139607183.83490777</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>140637660.28223953</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11530,7 +11663,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11695,6 +11828,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11704,7 +11840,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11869,6 +12005,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>56026187.499287754</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>57056663.946619511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11890,11 +12029,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="731821952"/>
-        <c:axId val="731829760"/>
+        <c:axId val="659891712"/>
+        <c:axId val="659893632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="731821952"/>
+        <c:axId val="659891712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11937,14 +12076,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="731829760"/>
+        <c:crossAx val="659893632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="731829760"/>
+        <c:axId val="659893632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11995,7 +12134,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="731821952"/>
+        <c:crossAx val="659891712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12709,7 +12848,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15162,6 +15301,44 @@
         <v>628259.51158101915</v>
       </c>
     </row>
+    <row r="58" spans="1:12" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="15">
+        <v>12659943.042425262</v>
+      </c>
+      <c r="H58" s="15">
+        <v>13571459.279536832</v>
+      </c>
+      <c r="I58" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J58" s="15">
+        <v>14329709.596181171</v>
+      </c>
+      <c r="K58" s="15">
+        <v>4968374.7784537468</v>
+      </c>
+      <c r="L58" s="14">
+        <v>758250.31664433924</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15178,7 +15355,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15213,13 +15390,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -15249,10 +15426,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15273,7 +15450,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -18948,6 +19125,71 @@
       </c>
       <c r="U57" s="11">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="15">
+        <v>13544471.519235244</v>
+      </c>
+      <c r="H58" s="15">
+        <v>14519673.830296591</v>
+      </c>
+      <c r="I58" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J58" s="15">
+        <v>15403573.839066558</v>
+      </c>
+      <c r="K58" s="15">
+        <v>5395800.2995436862</v>
+      </c>
+      <c r="L58" s="14">
+        <v>883900.00876996701</v>
+      </c>
+      <c r="M58" s="23">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="N58" s="23">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="O58" s="23">
+        <v>1.0756666660308838</v>
+      </c>
+      <c r="P58" s="23">
+        <v>0.904595238821847</v>
+      </c>
+      <c r="Q58" s="23">
+        <v>0.17107142720903679</v>
+      </c>
+      <c r="R58" s="23">
+        <v>0.11863264907785012</v>
+      </c>
+      <c r="S58" s="9">
+        <v>1.7794897361677517E-3</v>
+      </c>
+      <c r="T58" s="9">
+        <v>96.135101952006963</v>
+      </c>
+      <c r="U58" s="11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -18966,7 +19208,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19004,10 +19246,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -21735,6 +21977,50 @@
         <v>38.003913332402767</v>
       </c>
       <c r="N57" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="15">
+        <v>13494676.161662014</v>
+      </c>
+      <c r="H58" s="15">
+        <v>14466293.205648409</v>
+      </c>
+      <c r="I58" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J58" s="15">
+        <v>15282313.065362198</v>
+      </c>
+      <c r="K58" s="15">
+        <v>5319527.6861122884</v>
+      </c>
+      <c r="L58" s="14">
+        <v>816019.85971378826</v>
+      </c>
+      <c r="M58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="N58" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21754,7 +22040,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -21792,10 +22078,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -21828,7 +22114,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -24523,6 +24809,50 @@
         <v>38.003913332402767</v>
       </c>
       <c r="N57" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-745710.74747990887</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-695625.6799484134</v>
+      </c>
+      <c r="G58" s="15">
+        <v>122634814.91739957</v>
+      </c>
+      <c r="H58" s="15">
+        <v>131464524.86615519</v>
+      </c>
+      <c r="I58" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J58" s="15">
+        <v>136361067.73708206</v>
+      </c>
+      <c r="K58" s="15">
+        <v>48921115.074479356</v>
+      </c>
+      <c r="L58" s="14">
+        <v>4896542.8709268663</v>
+      </c>
+      <c r="M58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="N58" s="9">
         <v>1</v>
       </c>
     </row>
@@ -24542,7 +24872,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI57"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24580,19 +24910,19 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -24613,7 +24943,7 @@
         <v>16</v>
       </c>
       <c r="M1" s="27" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="N1" s="28" t="s">
         <v>18</v>
@@ -24622,7 +24952,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -27649,6 +27979,56 @@
         <v>38.003913332402767</v>
       </c>
       <c r="P57" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="14">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="14">
+        <v>-637497.67999171233</v>
+      </c>
+      <c r="H58" s="15">
+        <v>-594680.65682091936</v>
+      </c>
+      <c r="I58" s="15">
+        <v>128214614.22015479</v>
+      </c>
+      <c r="J58" s="15">
+        <v>137446069.86770549</v>
+      </c>
+      <c r="K58" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L58" s="15">
+        <v>140637660.28223953</v>
+      </c>
+      <c r="M58" s="15">
+        <v>57056663.946619511</v>
+      </c>
+      <c r="N58" s="14">
+        <v>3191590.4145340412</v>
+      </c>
+      <c r="O58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="P58" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,10 +133,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -161,10 +157,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -177,16 +169,16 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>标志</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>深创100ETF</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>成交量</t>
@@ -617,7 +609,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -785,6 +777,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,7 +789,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -961,6 +956,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1004,7 +1002,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1172,6 +1170,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1181,7 +1182,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1349,6 +1350,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>14329709.596181171</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14367689.690924622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1391,7 +1395,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1559,6 +1563,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1568,7 +1575,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1736,6 +1743,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4968374.7784537468</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5006354.8731971979</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1757,11 +1767,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90875008"/>
-        <c:axId val="90882048"/>
+        <c:axId val="106325120"/>
+        <c:axId val="106332160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90875008"/>
+        <c:axId val="106325120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1804,14 +1814,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90882048"/>
+        <c:crossAx val="106332160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90882048"/>
+        <c:axId val="106332160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1862,7 +1872,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90875008"/>
+        <c:crossAx val="106325120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2053,7 +2063,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2221,6 +2231,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-637497.67999171233</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-313710.67019325693</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2235,8 +2248,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="563940352"/>
-        <c:axId val="563938816"/>
+        <c:axId val="616985728"/>
+        <c:axId val="616966400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2261,7 +2274,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2429,6 +2442,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2438,7 +2454,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2606,6 +2622,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2622,11 +2641,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="542664960"/>
-        <c:axId val="563937280"/>
+        <c:axId val="616200448"/>
+        <c:axId val="616964864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="542664960"/>
+        <c:axId val="616200448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2669,14 +2688,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="563937280"/>
+        <c:crossAx val="616964864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="563937280"/>
+        <c:axId val="616964864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2727,12 +2746,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="542664960"/>
+        <c:crossAx val="616200448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="563938816"/>
+        <c:axId val="616966400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2769,12 +2788,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="563940352"/>
+        <c:crossAx val="616985728"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="563940352"/>
+        <c:axId val="616985728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2783,7 +2802,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="563938816"/>
+        <c:crossAx val="616966400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2945,7 +2964,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3113,6 +3132,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3127,8 +3149,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="564147328"/>
-        <c:axId val="382270080"/>
+        <c:axId val="541237632"/>
+        <c:axId val="538583808"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3153,7 +3175,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3321,6 +3343,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3330,7 +3355,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3498,6 +3523,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3514,11 +3542,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="91220224"/>
-        <c:axId val="382268160"/>
+        <c:axId val="524010240"/>
+        <c:axId val="524012160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="91220224"/>
+        <c:axId val="524010240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3561,14 +3589,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="382268160"/>
+        <c:crossAx val="524012160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="382268160"/>
+        <c:axId val="524012160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3619,12 +3647,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91220224"/>
+        <c:crossAx val="524010240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="382270080"/>
+        <c:axId val="538583808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3661,12 +3689,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564147328"/>
+        <c:crossAx val="541237632"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="564147328"/>
+        <c:axId val="541237632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3675,7 +3703,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="382270080"/>
+        <c:crossAx val="538583808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3854,7 +3882,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4022,6 +4050,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4031,7 +4062,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4198,6 +4229,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4241,7 +4275,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4409,6 +4443,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4418,7 +4455,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4586,6 +4623,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>15403573.839066558</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15444207.537798585</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4628,7 +4668,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4796,6 +4836,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4805,7 +4848,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4973,6 +5016,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5395800.2995436862</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5436433.998275714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4994,11 +5040,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="624962176"/>
-        <c:axId val="648290304"/>
+        <c:axId val="549655680"/>
+        <c:axId val="549657984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="624962176"/>
+        <c:axId val="549655680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5041,14 +5087,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="648290304"/>
+        <c:crossAx val="549657984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="648290304"/>
+        <c:axId val="549657984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5099,7 +5145,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624962176"/>
+        <c:crossAx val="549655680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5290,7 +5336,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5458,6 +5504,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5472,8 +5521,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="654992512"/>
-        <c:axId val="648334336"/>
+        <c:axId val="607760768"/>
+        <c:axId val="607758976"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5498,7 +5547,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5666,6 +5715,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5675,7 +5727,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5843,6 +5895,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5859,11 +5914,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="648310144"/>
-        <c:axId val="648332416"/>
+        <c:axId val="607747072"/>
+        <c:axId val="607757056"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="648310144"/>
+        <c:axId val="607747072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5906,14 +5961,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="648332416"/>
+        <c:crossAx val="607757056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="648332416"/>
+        <c:axId val="607757056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5964,12 +6019,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="648310144"/>
+        <c:crossAx val="607747072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="648334336"/>
+        <c:axId val="607758976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6006,12 +6061,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="654992512"/>
+        <c:crossAx val="607760768"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="654992512"/>
+        <c:axId val="607760768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6020,7 +6075,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="648334336"/>
+        <c:crossAx val="607758976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6199,7 +6254,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6367,6 +6422,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6376,7 +6434,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6543,6 +6601,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6586,7 +6647,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6754,6 +6815,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6763,7 +6827,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6931,6 +6995,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>15282313.065362198</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15322797.376976756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6973,7 +7040,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7141,6 +7208,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7150,7 +7220,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7318,6 +7388,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5319527.6861122884</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5360011.9977268465</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7339,11 +7412,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="655176064"/>
-        <c:axId val="655178368"/>
+        <c:axId val="611412224"/>
+        <c:axId val="611422208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="655176064"/>
+        <c:axId val="611412224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7386,14 +7459,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="655178368"/>
+        <c:crossAx val="611422208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="655178368"/>
+        <c:axId val="611422208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7444,7 +7517,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="655176064"/>
+        <c:crossAx val="611412224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7635,7 +7708,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7803,6 +7876,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7817,8 +7893,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="656342400"/>
-        <c:axId val="656340480"/>
+        <c:axId val="611529472"/>
+        <c:axId val="611449856"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7843,7 +7919,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8011,6 +8087,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8020,7 +8099,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8188,6 +8267,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8204,11 +8286,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="656315904"/>
-        <c:axId val="656338944"/>
+        <c:axId val="611437952"/>
+        <c:axId val="611448320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="656315904"/>
+        <c:axId val="611437952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8251,14 +8333,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656338944"/>
+        <c:crossAx val="611448320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="656338944"/>
+        <c:axId val="611448320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8309,12 +8391,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656315904"/>
+        <c:crossAx val="611437952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="656340480"/>
+        <c:axId val="611449856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8351,12 +8433,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656342400"/>
+        <c:crossAx val="611529472"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="656342400"/>
+        <c:axId val="611529472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8365,7 +8447,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="656340480"/>
+        <c:crossAx val="611449856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8544,7 +8626,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8712,6 +8794,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8721,7 +8806,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8888,6 +8973,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8931,7 +9019,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9099,6 +9187,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9108,7 +9199,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9276,6 +9367,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>136361067.73708206</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>136728974.75481507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9318,7 +9412,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9486,6 +9580,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9495,7 +9592,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9663,6 +9760,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>48921115.074479356</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>49289022.092212364</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9684,11 +9784,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="656405632"/>
-        <c:axId val="656560128"/>
+        <c:axId val="611942784"/>
+        <c:axId val="611944320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="656405632"/>
+        <c:axId val="611942784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9731,14 +9831,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656560128"/>
+        <c:crossAx val="611944320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="656560128"/>
+        <c:axId val="611944320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9789,7 +9889,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656405632"/>
+        <c:crossAx val="611942784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9980,7 +10080,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10148,6 +10248,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>122634814.91739957</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>122020082.29885046</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10162,8 +10265,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="659614336"/>
-        <c:axId val="659612416"/>
+        <c:axId val="613411456"/>
+        <c:axId val="613409536"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10188,7 +10291,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10356,6 +10459,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10365,7 +10471,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10533,6 +10639,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10549,11 +10658,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="657760640"/>
-        <c:axId val="657762944"/>
+        <c:axId val="613393536"/>
+        <c:axId val="613395456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="657760640"/>
+        <c:axId val="613393536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10596,14 +10705,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="657762944"/>
+        <c:crossAx val="613395456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="657762944"/>
+        <c:axId val="613395456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10654,12 +10763,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="657760640"/>
+        <c:crossAx val="613393536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="659612416"/>
+        <c:axId val="613409536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10696,12 +10805,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="659614336"/>
+        <c:crossAx val="613411456"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="659614336"/>
+        <c:axId val="613411456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10710,7 +10819,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="659612416"/>
+        <c:crossAx val="613409536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10889,7 +10998,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11057,6 +11166,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11066,7 +11178,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11233,6 +11345,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11276,7 +11391,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11444,6 +11559,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11453,7 +11571,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11621,6 +11739,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>140637660.28223953</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>141022306.81494966</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11663,7 +11784,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11831,6 +11952,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11840,7 +11964,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12008,6 +12132,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>57056663.946619511</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57441310.479329646</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12029,11 +12156,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="659891712"/>
-        <c:axId val="659893632"/>
+        <c:axId val="613474688"/>
+        <c:axId val="613476608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="659891712"/>
+        <c:axId val="613474688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12076,14 +12203,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="659893632"/>
+        <c:crossAx val="613476608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="659893632"/>
+        <c:axId val="613476608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12134,7 +12261,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="659891712"/>
+        <c:crossAx val="613474688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12848,7 +12975,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -12979,28 +13106,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -15337,6 +15464,44 @@
       </c>
       <c r="L58" s="14">
         <v>758250.31664433924</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="15">
+        <v>12548379.99314902</v>
+      </c>
+      <c r="H59" s="15">
+        <v>13489509.090988582</v>
+      </c>
+      <c r="I59" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J59" s="15">
+        <v>14367689.690924622</v>
+      </c>
+      <c r="K59" s="15">
+        <v>5006354.8731971979</v>
+      </c>
+      <c r="L59" s="14">
+        <v>878180.59993604012</v>
       </c>
     </row>
   </sheetData>
@@ -15355,7 +15520,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15393,7 +15558,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
         <v>9</v>
@@ -15426,10 +15591,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15450,7 +15615,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -15530,28 +15695,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="X3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -19189,6 +19354,71 @@
         <v>96.135101952006963</v>
       </c>
       <c r="U58" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="15">
+        <v>13432908.469959002</v>
+      </c>
+      <c r="H59" s="15">
+        <v>14440377.245736917</v>
+      </c>
+      <c r="I59" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J59" s="15">
+        <v>15444207.537798585</v>
+      </c>
+      <c r="K59" s="15">
+        <v>5436433.998275714</v>
+      </c>
+      <c r="L59" s="14">
+        <v>1003830.2920616679</v>
+      </c>
+      <c r="M59" s="23">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="N59" s="23">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="O59" s="23">
+        <v>1.071333368619283</v>
+      </c>
+      <c r="P59" s="23">
+        <v>0.92366667020888549</v>
+      </c>
+      <c r="Q59" s="23">
+        <v>0.14766669841039748</v>
+      </c>
+      <c r="R59" s="23">
+        <v>0.1233809505190168</v>
+      </c>
+      <c r="S59" s="9">
+        <v>1.850714257785252E-3</v>
+      </c>
+      <c r="T59" s="9">
+        <v>79.789031607240162</v>
+      </c>
+      <c r="U59" s="11">
         <v>1</v>
       </c>
     </row>
@@ -19208,7 +19438,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19243,10 +19473,10 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
         <v>9</v>
@@ -19282,7 +19512,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -19349,28 +19579,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -22021,6 +22251,50 @@
         <v>-130.04693515337254</v>
       </c>
       <c r="N58" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="15">
+        <v>13383113.112385772</v>
+      </c>
+      <c r="H59" s="15">
+        <v>14386847.233971268</v>
+      </c>
+      <c r="I59" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J59" s="15">
+        <v>15322797.376976756</v>
+      </c>
+      <c r="K59" s="15">
+        <v>5360011.9977268465</v>
+      </c>
+      <c r="L59" s="14">
+        <v>935950.14300548914</v>
+      </c>
+      <c r="M59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="N59" s="9">
         <v>1</v>
       </c>
     </row>
@@ -22040,7 +22314,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22078,10 +22352,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -22181,28 +22455,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -24853,6 +25127,50 @@
         <v>-130.04693515337254</v>
       </c>
       <c r="N58" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-660837.59425302898</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-614732.61854911025</v>
+      </c>
+      <c r="G59" s="15">
+        <v>122020082.29885046</v>
+      </c>
+      <c r="H59" s="15">
+        <v>131171594.28963518</v>
+      </c>
+      <c r="I59" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J59" s="15">
+        <v>136728974.75481507</v>
+      </c>
+      <c r="K59" s="15">
+        <v>49289022.092212364</v>
+      </c>
+      <c r="L59" s="14">
+        <v>5557380.4651798951</v>
+      </c>
+      <c r="M59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="N59" s="9">
         <v>1</v>
       </c>
     </row>
@@ -24872,7 +25190,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI58"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24907,10 +25225,10 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1" s="25" t="s">
         <v>9</v>
@@ -24919,10 +25237,10 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -24952,7 +25270,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -25027,28 +25345,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="V3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -28029,6 +28347,56 @@
         <v>-130.04693515337254</v>
       </c>
       <c r="P58" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="14">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="14">
+        <v>-313710.67019325693</v>
+      </c>
+      <c r="H59" s="15">
+        <v>-291823.86630512617</v>
+      </c>
+      <c r="I59" s="15">
+        <v>127922790.35384966</v>
+      </c>
+      <c r="J59" s="15">
+        <v>137517005.73022237</v>
+      </c>
+      <c r="K59" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L59" s="15">
+        <v>141022306.81494966</v>
+      </c>
+      <c r="M59" s="15">
+        <v>57441310.479329646</v>
+      </c>
+      <c r="N59" s="14">
+        <v>3505301.084727298</v>
+      </c>
+      <c r="O59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="P59" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="30">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -167,18 +167,6 @@
   <si>
     <t>标志</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>标志</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>成交量</t>
@@ -609,7 +597,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -780,6 +768,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -789,7 +780,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -959,6 +950,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1002,7 +996,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1173,6 +1167,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1182,7 +1179,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1353,6 +1350,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14367689.690924622</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14028882.557513656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1395,7 +1395,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1566,6 +1566,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1575,7 +1578,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1746,6 +1749,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5006354.8731971979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4667547.7397862319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1767,11 +1773,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="106325120"/>
-        <c:axId val="106332160"/>
+        <c:axId val="80006144"/>
+        <c:axId val="80195968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="106325120"/>
+        <c:axId val="80006144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1814,14 +1820,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="106332160"/>
+        <c:crossAx val="80195968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="106332160"/>
+        <c:axId val="80195968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1872,7 +1878,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="106325120"/>
+        <c:crossAx val="80006144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2063,7 +2069,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2234,6 +2240,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-313710.67019325693</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-166564.10795343228</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2248,8 +2257,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="616985728"/>
-        <c:axId val="616966400"/>
+        <c:axId val="566072064"/>
+        <c:axId val="566012928"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2274,7 +2283,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2445,6 +2454,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2454,7 +2466,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2625,6 +2637,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2641,11 +2656,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="616200448"/>
-        <c:axId val="616964864"/>
+        <c:axId val="566007680"/>
+        <c:axId val="566010240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="616200448"/>
+        <c:axId val="566007680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2688,14 +2703,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616964864"/>
+        <c:crossAx val="566010240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="616964864"/>
+        <c:axId val="566010240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2746,12 +2761,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616200448"/>
+        <c:crossAx val="566007680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="616966400"/>
+        <c:axId val="566012928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2788,12 +2803,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616985728"/>
+        <c:crossAx val="566072064"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="616985728"/>
+        <c:axId val="566072064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2802,7 +2817,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="616966400"/>
+        <c:crossAx val="566012928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2964,7 +2979,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3135,6 +3150,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3149,8 +3167,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="541237632"/>
-        <c:axId val="538583808"/>
+        <c:axId val="527064448"/>
+        <c:axId val="526452992"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3175,7 +3193,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3346,6 +3364,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3355,7 +3376,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3526,6 +3547,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3542,11 +3566,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="524010240"/>
-        <c:axId val="524012160"/>
+        <c:axId val="476680192"/>
+        <c:axId val="526228096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="524010240"/>
+        <c:axId val="476680192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3589,14 +3613,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524012160"/>
+        <c:crossAx val="526228096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="524012160"/>
+        <c:axId val="526228096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3647,12 +3671,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524010240"/>
+        <c:crossAx val="476680192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="538583808"/>
+        <c:axId val="526452992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3689,12 +3713,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541237632"/>
+        <c:crossAx val="527064448"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="541237632"/>
+        <c:axId val="527064448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3703,7 +3727,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="538583808"/>
+        <c:crossAx val="526452992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3882,7 +3906,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4053,6 +4077,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4062,7 +4089,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4232,6 +4259,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4275,7 +4305,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4446,6 +4476,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4455,7 +4488,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4626,6 +4659,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>15444207.537798585</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>15081518.073934447</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4668,7 +4704,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4839,6 +4875,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4848,7 +4887,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5019,6 +5058,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5436433.998275714</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5073744.5344115756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5040,11 +5082,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="549655680"/>
-        <c:axId val="549657984"/>
+        <c:axId val="556883968"/>
+        <c:axId val="556885504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="549655680"/>
+        <c:axId val="556883968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5087,14 +5129,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="549657984"/>
+        <c:crossAx val="556885504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="549657984"/>
+        <c:axId val="556885504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5145,7 +5187,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="549655680"/>
+        <c:crossAx val="556883968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5336,7 +5378,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5507,6 +5549,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5521,8 +5566,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="607760768"/>
-        <c:axId val="607758976"/>
+        <c:axId val="558842624"/>
+        <c:axId val="558828160"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5547,7 +5592,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5718,6 +5763,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5727,7 +5775,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5898,6 +5946,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5914,11 +5965,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="607747072"/>
-        <c:axId val="607757056"/>
+        <c:axId val="556912000"/>
+        <c:axId val="558826624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="607747072"/>
+        <c:axId val="556912000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5961,14 +6012,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="607757056"/>
+        <c:crossAx val="558826624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="607757056"/>
+        <c:axId val="558826624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6019,12 +6070,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="607747072"/>
+        <c:crossAx val="556912000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="607758976"/>
+        <c:axId val="558828160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6061,12 +6112,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="607760768"/>
+        <c:crossAx val="558842624"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="607760768"/>
+        <c:axId val="558842624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6075,7 +6126,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="607758976"/>
+        <c:crossAx val="558828160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6254,7 +6305,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6425,6 +6476,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6434,7 +6488,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6604,6 +6658,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6647,7 +6704,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6818,6 +6875,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6827,7 +6887,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6998,6 +7058,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>15322797.376976756</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14961452.391233759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7040,7 +7103,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7211,6 +7274,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7220,7 +7286,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7391,6 +7457,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5360011.9977268465</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4998667.0119838491</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7412,11 +7481,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="611412224"/>
-        <c:axId val="611422208"/>
+        <c:axId val="558861312"/>
+        <c:axId val="558879488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="611412224"/>
+        <c:axId val="558861312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7459,14 +7528,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611422208"/>
+        <c:crossAx val="558879488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="611422208"/>
+        <c:axId val="558879488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7517,7 +7586,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611412224"/>
+        <c:crossAx val="558861312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7708,7 +7777,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7879,6 +7948,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7893,8 +7965,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="611529472"/>
-        <c:axId val="611449856"/>
+        <c:axId val="561834240"/>
+        <c:axId val="561832704"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7919,7 +7991,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8090,6 +8162,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8099,7 +8174,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8270,6 +8345,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8286,11 +8364,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="611437952"/>
-        <c:axId val="611448320"/>
+        <c:axId val="558949504"/>
+        <c:axId val="558951424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="611437952"/>
+        <c:axId val="558949504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8333,14 +8411,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611448320"/>
+        <c:crossAx val="558951424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="611448320"/>
+        <c:axId val="558951424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8391,12 +8469,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611437952"/>
+        <c:crossAx val="558949504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="611449856"/>
+        <c:axId val="561832704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8433,12 +8511,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611529472"/>
+        <c:crossAx val="561834240"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="611529472"/>
+        <c:axId val="561834240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8447,7 +8525,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="611449856"/>
+        <c:crossAx val="561832704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8626,7 +8704,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8797,6 +8875,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8806,7 +8887,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8976,6 +9057,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9019,7 +9103,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9190,6 +9274,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9199,7 +9286,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9370,6 +9457,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>136728974.75481507</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>133434424.03792456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9412,7 +9502,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9583,6 +9673,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9592,7 +9685,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9763,6 +9856,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>49289022.092212364</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>45994471.37532185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9784,11 +9880,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="611942784"/>
-        <c:axId val="611944320"/>
+        <c:axId val="562050176"/>
+        <c:axId val="562052096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="611942784"/>
+        <c:axId val="562050176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9831,14 +9927,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611944320"/>
+        <c:crossAx val="562052096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="611944320"/>
+        <c:axId val="562052096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9889,7 +9985,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611942784"/>
+        <c:crossAx val="562050176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10080,7 +10176,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10251,6 +10347,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>122020082.29885046</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>121696158.60682116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10265,8 +10364,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="613411456"/>
-        <c:axId val="613409536"/>
+        <c:axId val="562758784"/>
+        <c:axId val="562514560"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10291,7 +10390,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10462,6 +10561,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10471,7 +10573,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10642,6 +10744,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10658,11 +10763,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="613393536"/>
-        <c:axId val="613395456"/>
+        <c:axId val="562486272"/>
+        <c:axId val="562512640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="613393536"/>
+        <c:axId val="562486272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10705,14 +10810,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613395456"/>
+        <c:crossAx val="562512640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="613395456"/>
+        <c:axId val="562512640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10763,12 +10868,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613393536"/>
+        <c:crossAx val="562486272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="613409536"/>
+        <c:axId val="562514560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10805,12 +10910,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613411456"/>
+        <c:crossAx val="562758784"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="613411456"/>
+        <c:axId val="562758784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10819,7 +10924,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="613409536"/>
+        <c:crossAx val="562514560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10998,7 +11103,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11169,6 +11274,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11178,7 +11286,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11348,6 +11456,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11391,7 +11502,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11562,6 +11673,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11571,7 +11685,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11742,6 +11856,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>141022306.81494966</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>137568382.5696381</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11784,7 +11901,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11955,6 +12072,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11964,7 +12084,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12135,6 +12255,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>57441310.479329646</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>53987386.234018087</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12156,11 +12279,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="613474688"/>
-        <c:axId val="613476608"/>
+        <c:axId val="564680960"/>
+        <c:axId val="565166080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="613474688"/>
+        <c:axId val="564680960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12203,14 +12326,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613476608"/>
+        <c:crossAx val="565166080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="613476608"/>
+        <c:axId val="565166080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12261,7 +12384,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613474688"/>
+        <c:crossAx val="564680960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12975,7 +13098,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15504,6 +15627,44 @@
         <v>878180.59993604012</v>
       </c>
     </row>
+    <row r="60" spans="1:12" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="15">
+        <v>12474978.130078416</v>
+      </c>
+      <c r="H60" s="15">
+        <v>13073776.806689657</v>
+      </c>
+      <c r="I60" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J60" s="15">
+        <v>14028882.557513656</v>
+      </c>
+      <c r="K60" s="15">
+        <v>4667547.7397862319</v>
+      </c>
+      <c r="L60" s="14">
+        <v>955105.75082399882</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15520,7 +15681,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM59"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19422,6 +19583,71 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:21" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="15">
+        <v>13359506.606888399</v>
+      </c>
+      <c r="H60" s="15">
+        <v>14000762.63098482</v>
+      </c>
+      <c r="I60" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J60" s="15">
+        <v>15081518.073934447</v>
+      </c>
+      <c r="K60" s="15">
+        <v>5073744.5344115756</v>
+      </c>
+      <c r="L60" s="14">
+        <v>1080755.4429496266</v>
+      </c>
+      <c r="M60" s="23">
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="N60" s="23">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="O60" s="23">
+        <v>1.0603333314259846</v>
+      </c>
+      <c r="P60" s="23">
+        <v>0.94423809789475943</v>
+      </c>
+      <c r="Q60" s="23">
+        <v>0.11609523353122519</v>
+      </c>
+      <c r="R60" s="23">
+        <v>0.11939455619474655</v>
+      </c>
+      <c r="S60" s="9">
+        <v>1.7909183429211982E-3</v>
+      </c>
+      <c r="T60" s="9">
+        <v>64.824414798198021</v>
+      </c>
+      <c r="U60" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19438,7 +19664,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19473,7 +19699,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -22295,6 +22521,50 @@
         <v>38.965935849742465</v>
       </c>
       <c r="N59" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="15">
+        <v>13309711.249315169</v>
+      </c>
+      <c r="H60" s="15">
+        <v>13948577.097340312</v>
+      </c>
+      <c r="I60" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J60" s="15">
+        <v>14961452.391233759</v>
+      </c>
+      <c r="K60" s="15">
+        <v>4998667.0119838491</v>
+      </c>
+      <c r="L60" s="14">
+        <v>1012875.2938934478</v>
+      </c>
+      <c r="M60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="N60" s="9">
         <v>1</v>
       </c>
     </row>
@@ -22314,7 +22584,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22388,7 +22658,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -25171,6 +25441,50 @@
         <v>38.965935849742465</v>
       </c>
       <c r="N59" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-339472.02214159875</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-323923.69202929962</v>
+      </c>
+      <c r="G60" s="15">
+        <v>121696158.60682116</v>
+      </c>
+      <c r="H60" s="15">
+        <v>127537571.55060306</v>
+      </c>
+      <c r="I60" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J60" s="15">
+        <v>133434424.03792456</v>
+      </c>
+      <c r="K60" s="15">
+        <v>45994471.37532185</v>
+      </c>
+      <c r="L60" s="14">
+        <v>5896852.4873214941</v>
+      </c>
+      <c r="M60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="N60" s="9">
         <v>1</v>
       </c>
     </row>
@@ -25190,7 +25504,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25225,10 +25539,10 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
         <v>9</v>
@@ -25237,10 +25551,10 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -28397,6 +28711,56 @@
         <v>38.965935849742465</v>
       </c>
       <c r="P59" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="14">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="14">
+        <v>-166564.10795343228</v>
+      </c>
+      <c r="H60" s="15">
+        <v>-158935.2208393114</v>
+      </c>
+      <c r="I60" s="15">
+        <v>127763855.13301036</v>
+      </c>
+      <c r="J60" s="15">
+        <v>133896517.37695739</v>
+      </c>
+      <c r="K60" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L60" s="15">
+        <v>137568382.5696381</v>
+      </c>
+      <c r="M60" s="15">
+        <v>53987386.234018087</v>
+      </c>
+      <c r="N60" s="14">
+        <v>3671865.1926807305</v>
+      </c>
+      <c r="O60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="P60" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,6 +133,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -157,6 +161,14 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -166,6 +178,14 @@
   </si>
   <si>
     <t>标志</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>标志</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -597,7 +617,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -771,6 +791,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -780,7 +803,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -953,6 +976,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -996,7 +1022,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1170,6 +1196,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1179,7 +1208,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1353,6 +1382,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14028882.557513656</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15638155.580985475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1395,7 +1427,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1569,6 +1601,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1578,7 +1613,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1752,6 +1787,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4667547.7397862319</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6276820.7632580511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1773,11 +1811,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80006144"/>
-        <c:axId val="80195968"/>
+        <c:axId val="346878720"/>
+        <c:axId val="346923008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80006144"/>
+        <c:axId val="346878720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1820,14 +1858,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80195968"/>
+        <c:crossAx val="346923008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80195968"/>
+        <c:axId val="346923008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1878,7 +1916,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80006144"/>
+        <c:crossAx val="346878720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2069,7 +2107,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2243,6 +2281,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-166564.10795343228</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-848400.08660027001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2257,8 +2298,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566072064"/>
-        <c:axId val="566012928"/>
+        <c:axId val="593609856"/>
+        <c:axId val="593505664"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2283,7 +2324,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2457,6 +2498,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2466,7 +2510,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2640,6 +2684,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2656,11 +2703,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566007680"/>
-        <c:axId val="566010240"/>
+        <c:axId val="593502208"/>
+        <c:axId val="593503744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566007680"/>
+        <c:axId val="593502208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2703,14 +2750,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566010240"/>
+        <c:crossAx val="593503744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566010240"/>
+        <c:axId val="593503744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2761,12 +2808,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566007680"/>
+        <c:crossAx val="593502208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566012928"/>
+        <c:axId val="593505664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2803,12 +2850,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566072064"/>
+        <c:crossAx val="593609856"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566072064"/>
+        <c:axId val="593609856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2817,7 +2864,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566012928"/>
+        <c:crossAx val="593505664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2979,7 +3026,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3153,6 +3200,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3167,8 +3217,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="527064448"/>
-        <c:axId val="526452992"/>
+        <c:axId val="347069824"/>
+        <c:axId val="347067904"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3193,7 +3243,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3367,6 +3417,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3376,7 +3429,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3550,6 +3603,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3566,11 +3622,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="476680192"/>
-        <c:axId val="526228096"/>
+        <c:axId val="347021696"/>
+        <c:axId val="347024000"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="476680192"/>
+        <c:axId val="347021696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3613,14 +3669,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526228096"/>
+        <c:crossAx val="347024000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526228096"/>
+        <c:axId val="347024000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3671,12 +3727,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="476680192"/>
+        <c:crossAx val="347021696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="526452992"/>
+        <c:axId val="347067904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3713,12 +3769,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527064448"/>
+        <c:crossAx val="347069824"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="527064448"/>
+        <c:axId val="347069824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3727,7 +3783,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="526452992"/>
+        <c:crossAx val="347067904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3906,7 +3962,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4080,6 +4136,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4089,7 +4148,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4262,6 +4321,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4305,7 +4367,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4479,6 +4541,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4488,7 +4553,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4662,6 +4727,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>15081518.073934447</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16804895.330806952</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4704,7 +4772,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4878,6 +4946,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4887,7 +4958,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5061,6 +5132,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5073744.5344115756</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6797121.7912840806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5082,11 +5156,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556883968"/>
-        <c:axId val="556885504"/>
+        <c:axId val="347482368"/>
+        <c:axId val="347616384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556883968"/>
+        <c:axId val="347482368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5129,14 +5203,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556885504"/>
+        <c:crossAx val="347616384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556885504"/>
+        <c:axId val="347616384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5187,7 +5261,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556883968"/>
+        <c:crossAx val="347482368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5378,7 +5452,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5552,6 +5626,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5566,8 +5643,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="558842624"/>
-        <c:axId val="558828160"/>
+        <c:axId val="443928960"/>
+        <c:axId val="443837056"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5592,7 +5669,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5766,6 +5843,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5775,7 +5855,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5949,6 +6029,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5965,11 +6048,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556912000"/>
-        <c:axId val="558826624"/>
+        <c:axId val="443832576"/>
+        <c:axId val="443835520"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556912000"/>
+        <c:axId val="443832576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6012,14 +6095,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558826624"/>
+        <c:crossAx val="443835520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558826624"/>
+        <c:axId val="443835520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6070,12 +6153,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556912000"/>
+        <c:crossAx val="443832576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="558828160"/>
+        <c:axId val="443837056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6112,12 +6195,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558842624"/>
+        <c:crossAx val="443928960"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="558842624"/>
+        <c:axId val="443928960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6126,7 +6209,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="558828160"/>
+        <c:crossAx val="443837056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6305,7 +6388,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6479,6 +6562,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6488,7 +6574,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6661,6 +6747,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6704,7 +6793,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6878,6 +6967,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6887,7 +6979,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7061,6 +7153,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14961452.391233759</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16678406.043607632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7103,7 +7198,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7277,6 +7372,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7286,7 +7384,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7460,6 +7558,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4998667.0119838491</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6715620.6643577218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7481,11 +7582,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="558861312"/>
-        <c:axId val="558879488"/>
+        <c:axId val="443960704"/>
+        <c:axId val="443966592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="558861312"/>
+        <c:axId val="443960704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7528,14 +7629,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558879488"/>
+        <c:crossAx val="443966592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558879488"/>
+        <c:axId val="443966592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7586,7 +7687,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558861312"/>
+        <c:crossAx val="443960704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7777,7 +7878,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7951,6 +8052,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,8 +8069,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="561834240"/>
-        <c:axId val="561832704"/>
+        <c:axId val="489323904"/>
+        <c:axId val="489321984"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7991,7 +8095,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8165,6 +8269,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8174,7 +8281,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8348,6 +8455,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8364,11 +8474,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="558949504"/>
-        <c:axId val="558951424"/>
+        <c:axId val="467541376"/>
+        <c:axId val="489320448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="558949504"/>
+        <c:axId val="467541376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8411,14 +8521,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558951424"/>
+        <c:crossAx val="489320448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558951424"/>
+        <c:axId val="489320448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8469,12 +8579,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558949504"/>
+        <c:crossAx val="467541376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="561832704"/>
+        <c:axId val="489321984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8511,12 +8621,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561834240"/>
+        <c:crossAx val="489323904"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="561834240"/>
+        <c:axId val="489323904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8525,7 +8635,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="561832704"/>
+        <c:crossAx val="489321984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8704,7 +8814,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8878,6 +8988,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8887,7 +9000,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9060,6 +9173,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9103,7 +9219,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9277,6 +9393,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9286,7 +9405,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9460,6 +9579,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>133434424.03792456</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>149133236.73835805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9502,7 +9624,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9676,6 +9798,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9685,7 +9810,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9859,6 +9984,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>45994471.37532185</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>61693284.075755343</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9880,11 +10008,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="562050176"/>
-        <c:axId val="562052096"/>
+        <c:axId val="565584256"/>
+        <c:axId val="565891840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="562050176"/>
+        <c:axId val="565584256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9927,14 +10055,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562052096"/>
+        <c:crossAx val="565891840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="562052096"/>
+        <c:axId val="565891840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9985,7 +10113,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562050176"/>
+        <c:crossAx val="565584256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10176,7 +10304,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10350,6 +10478,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>121696158.60682116</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>119779016.08311573</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10364,8 +10495,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="562758784"/>
-        <c:axId val="562514560"/>
+        <c:axId val="593340288"/>
+        <c:axId val="593338368"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10390,7 +10521,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10564,6 +10695,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10573,7 +10707,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10747,6 +10881,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10763,11 +10900,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="562486272"/>
-        <c:axId val="562512640"/>
+        <c:axId val="589926784"/>
+        <c:axId val="589928320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="562486272"/>
+        <c:axId val="589926784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10810,14 +10947,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562512640"/>
+        <c:crossAx val="589928320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="562512640"/>
+        <c:axId val="589928320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10868,12 +11005,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562486272"/>
+        <c:crossAx val="589926784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="562514560"/>
+        <c:axId val="593338368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10910,12 +11047,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562758784"/>
+        <c:crossAx val="593340288"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="562758784"/>
+        <c:axId val="593340288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10924,7 +11061,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="562514560"/>
+        <c:crossAx val="593338368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11103,7 +11240,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11277,6 +11414,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11286,7 +11426,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11459,6 +11599,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11502,7 +11645,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11676,6 +11819,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11685,7 +11831,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11859,6 +12005,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>137568382.5696381</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>154049928.53279907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11901,7 +12050,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12075,6 +12224,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12084,7 +12236,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12258,6 +12410,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>53987386.234018087</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>70468932.197179049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12279,11 +12434,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="564680960"/>
-        <c:axId val="565166080"/>
+        <c:axId val="593399808"/>
+        <c:axId val="593401344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="564680960"/>
+        <c:axId val="593399808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12326,14 +12481,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565166080"/>
+        <c:crossAx val="593401344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565166080"/>
+        <c:axId val="593401344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12384,7 +12539,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564680960"/>
+        <c:crossAx val="593399808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13098,7 +13253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -13229,28 +13384,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -15663,6 +15818,44 @@
       </c>
       <c r="L60" s="14">
         <v>955105.75082399882</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="15">
+        <v>12243926.091061944</v>
+      </c>
+      <c r="H61" s="15">
+        <v>14411101.569662364</v>
+      </c>
+      <c r="I61" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J61" s="15">
+        <v>15638155.580985475</v>
+      </c>
+      <c r="K61" s="15">
+        <v>6276820.7632580511</v>
+      </c>
+      <c r="L61" s="14">
+        <v>1227054.0113231102</v>
       </c>
     </row>
   </sheetData>
@@ -15681,7 +15874,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15719,10 +15912,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -15752,10 +15945,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15776,7 +15969,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -15856,28 +16049,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -19645,6 +19838,71 @@
         <v>64.824414798198021</v>
       </c>
       <c r="U60" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="15">
+        <v>13128454.567871926</v>
+      </c>
+      <c r="H61" s="15">
+        <v>15452191.627358215</v>
+      </c>
+      <c r="I61" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J61" s="15">
+        <v>16804895.330806952</v>
+      </c>
+      <c r="K61" s="15">
+        <v>6797121.7912840806</v>
+      </c>
+      <c r="L61" s="14">
+        <v>1352703.703448738</v>
+      </c>
+      <c r="M61" s="23">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="N61" s="23">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="O61" s="23">
+        <v>1.1330000162124634</v>
+      </c>
+      <c r="P61" s="23">
+        <v>0.9662142892678578</v>
+      </c>
+      <c r="Q61" s="23">
+        <v>0.16678572694460558</v>
+      </c>
+      <c r="R61" s="23">
+        <v>0.11951701130185809</v>
+      </c>
+      <c r="S61" s="9">
+        <v>1.7927551695278712E-3</v>
+      </c>
+      <c r="T61" s="9">
+        <v>93.033187007085431</v>
+      </c>
+      <c r="U61" s="11">
         <v>1</v>
       </c>
     </row>
@@ -19664,7 +19922,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19738,7 +19996,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -19805,28 +20063,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -22565,6 +22823,50 @@
         <v>-89.784897005371036</v>
       </c>
       <c r="N60" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="15">
+        <v>13078659.210298697</v>
+      </c>
+      <c r="H61" s="15">
+        <v>15393582.489215072</v>
+      </c>
+      <c r="I61" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J61" s="15">
+        <v>16678406.043607632</v>
+      </c>
+      <c r="K61" s="15">
+        <v>6715620.6643577218</v>
+      </c>
+      <c r="L61" s="14">
+        <v>1284823.5543925592</v>
+      </c>
+      <c r="M61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="N61" s="9">
         <v>1</v>
       </c>
     </row>
@@ -22584,7 +22886,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22625,7 +22927,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -22658,7 +22960,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -22725,28 +23027,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -25485,6 +25787,50 @@
         <v>-89.784897005371036</v>
       </c>
       <c r="N60" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-2256476.8381611248</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-1917142.5237054415</v>
+      </c>
+      <c r="G61" s="15">
+        <v>119779016.08311573</v>
+      </c>
+      <c r="H61" s="15">
+        <v>140979907.41287544</v>
+      </c>
+      <c r="I61" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J61" s="15">
+        <v>149133236.73835805</v>
+      </c>
+      <c r="K61" s="15">
+        <v>61693284.075755343</v>
+      </c>
+      <c r="L61" s="14">
+        <v>8153329.325482619</v>
+      </c>
+      <c r="M61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="N61" s="9">
         <v>1</v>
       </c>
     </row>
@@ -25504,7 +25850,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25545,16 +25891,16 @@
         <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -25584,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -25659,28 +26005,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -28761,6 +29107,56 @@
         <v>-89.784897005371036</v>
       </c>
       <c r="P60" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="14">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="14">
+        <v>-848400.08660027001</v>
+      </c>
+      <c r="H61" s="15">
+        <v>-720815.67850802618</v>
+      </c>
+      <c r="I61" s="15">
+        <v>127043039.45450233</v>
+      </c>
+      <c r="J61" s="15">
+        <v>149529663.25351807</v>
+      </c>
+      <c r="K61" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L61" s="15">
+        <v>154049928.53279907</v>
+      </c>
+      <c r="M61" s="15">
+        <v>70468932.197179049</v>
+      </c>
+      <c r="N61" s="14">
+        <v>4520265.2792810006</v>
+      </c>
+      <c r="O61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="P61" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,10 +133,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -161,14 +157,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -181,12 +169,20 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>标志</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>PE</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>成交量</t>
@@ -617,7 +613,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -794,6 +790,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -803,7 +802,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -979,6 +978,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1022,7 +1024,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1199,6 +1201,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1208,7 +1213,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1385,6 +1390,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>15638155.580985475</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16470742.053078819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1427,7 +1435,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1604,6 +1612,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1613,7 +1624,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1790,6 +1801,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6276820.7632580511</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7109407.2353513949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,11 +1825,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="346878720"/>
-        <c:axId val="346923008"/>
+        <c:axId val="402019072"/>
+        <c:axId val="402023936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="346878720"/>
+        <c:axId val="402019072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1858,14 +1872,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346923008"/>
+        <c:crossAx val="402023936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="346923008"/>
+        <c:axId val="402023936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1916,7 +1930,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346878720"/>
+        <c:crossAx val="402019072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2107,7 +2121,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2284,6 +2298,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-848400.08660027001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-2500093.7589145182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2298,8 +2315,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="593609856"/>
-        <c:axId val="593505664"/>
+        <c:axId val="624593920"/>
+        <c:axId val="624592384"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2324,7 +2341,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2501,6 +2518,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2510,7 +2530,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2687,6 +2707,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2703,11 +2726,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="593502208"/>
-        <c:axId val="593503744"/>
+        <c:axId val="624543616"/>
+        <c:axId val="624545152"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="593502208"/>
+        <c:axId val="624543616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2750,14 +2773,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593503744"/>
+        <c:crossAx val="624545152"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="593503744"/>
+        <c:axId val="624545152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2808,12 +2831,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593502208"/>
+        <c:crossAx val="624543616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="593505664"/>
+        <c:axId val="624592384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2850,12 +2873,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593609856"/>
+        <c:crossAx val="624593920"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="593609856"/>
+        <c:axId val="624593920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2864,7 +2887,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="593505664"/>
+        <c:crossAx val="624592384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3026,7 +3049,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3203,6 +3226,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3217,8 +3243,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="347069824"/>
-        <c:axId val="347067904"/>
+        <c:axId val="403247488"/>
+        <c:axId val="402060800"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3243,7 +3269,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3420,6 +3446,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3429,7 +3458,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3606,6 +3635,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3622,11 +3654,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="347021696"/>
-        <c:axId val="347024000"/>
+        <c:axId val="402048128"/>
+        <c:axId val="402049664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="347021696"/>
+        <c:axId val="402048128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3669,14 +3701,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="347024000"/>
+        <c:crossAx val="402049664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="347024000"/>
+        <c:axId val="402049664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3727,12 +3759,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="347021696"/>
+        <c:crossAx val="402048128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="347067904"/>
+        <c:axId val="402060800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3769,12 +3801,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="347069824"/>
+        <c:crossAx val="403247488"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="347069824"/>
+        <c:axId val="403247488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3783,7 +3815,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="347067904"/>
+        <c:crossAx val="402060800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3962,7 +3994,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4139,6 +4171,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4148,7 +4183,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4324,6 +4359,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4367,7 +4405,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4544,6 +4582,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4553,7 +4594,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4730,6 +4771,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>16804895.330806952</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17697629.703050636</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4772,7 +4816,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4949,6 +4993,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4958,7 +5005,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5135,6 +5182,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6797121.7912840806</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7689856.1635277644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5156,11 +5206,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="347482368"/>
-        <c:axId val="347616384"/>
+        <c:axId val="403298560"/>
+        <c:axId val="403300352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="347482368"/>
+        <c:axId val="403298560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5203,14 +5253,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="347616384"/>
+        <c:crossAx val="403300352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="347616384"/>
+        <c:axId val="403300352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5261,7 +5311,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="347482368"/>
+        <c:crossAx val="403298560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5452,7 +5502,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5629,6 +5679,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-394977.32401696721</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5643,8 +5696,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="443928960"/>
-        <c:axId val="443837056"/>
+        <c:axId val="617034112"/>
+        <c:axId val="571240832"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5669,7 +5722,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5846,6 +5899,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5855,7 +5911,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6032,6 +6088,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6048,11 +6107,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="443832576"/>
-        <c:axId val="443835520"/>
+        <c:axId val="494914176"/>
+        <c:axId val="546480512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="443832576"/>
+        <c:axId val="494914176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6095,14 +6154,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443835520"/>
+        <c:crossAx val="546480512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="443835520"/>
+        <c:axId val="546480512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6153,12 +6212,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443832576"/>
+        <c:crossAx val="494914176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="443837056"/>
+        <c:axId val="571240832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6195,12 +6254,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443928960"/>
+        <c:crossAx val="617034112"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="443928960"/>
+        <c:axId val="617034112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6209,7 +6268,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="443837056"/>
+        <c:crossAx val="571240832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6388,7 +6447,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6565,6 +6624,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6574,7 +6636,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6750,6 +6812,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6793,7 +6858,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6970,6 +7035,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6979,7 +7047,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7156,6 +7224,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>16678406.043607632</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17567754.333578344</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7198,7 +7269,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7375,6 +7446,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7384,7 +7458,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7561,6 +7635,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6715620.6643577218</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7604968.9543284345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7582,11 +7659,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="443960704"/>
-        <c:axId val="443966592"/>
+        <c:axId val="617065472"/>
+        <c:axId val="617071744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="443960704"/>
+        <c:axId val="617065472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7629,14 +7706,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443966592"/>
+        <c:crossAx val="617071744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="443966592"/>
+        <c:axId val="617071744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7687,7 +7764,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443960704"/>
+        <c:crossAx val="617065472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7878,7 +7955,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8055,6 +8132,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-394977.32401696721</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8069,8 +8149,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="489323904"/>
-        <c:axId val="489321984"/>
+        <c:axId val="621931904"/>
+        <c:axId val="621930368"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8095,7 +8175,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8272,6 +8352,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8281,7 +8364,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8458,6 +8541,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8474,11 +8560,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467541376"/>
-        <c:axId val="489320448"/>
+        <c:axId val="621893888"/>
+        <c:axId val="621928448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467541376"/>
+        <c:axId val="621893888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8521,14 +8607,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489320448"/>
+        <c:crossAx val="621928448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="489320448"/>
+        <c:axId val="621928448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8579,12 +8665,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467541376"/>
+        <c:crossAx val="621893888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="489321984"/>
+        <c:axId val="621930368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8621,12 +8707,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489323904"/>
+        <c:crossAx val="621931904"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="489323904"/>
+        <c:axId val="621931904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8635,7 +8721,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="489321984"/>
+        <c:crossAx val="621930368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8814,7 +8900,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8991,6 +9077,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9000,7 +9089,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9176,6 +9265,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9219,7 +9311,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9396,6 +9488,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9405,7 +9500,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9582,6 +9677,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>149133236.73835805</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>157278204.92011258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9624,7 +9722,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9801,6 +9899,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9810,7 +9911,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9987,6 +10088,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>61693284.075755343</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>69838252.257509872</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10008,11 +10112,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565584256"/>
-        <c:axId val="565891840"/>
+        <c:axId val="622215168"/>
+        <c:axId val="622217088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565584256"/>
+        <c:axId val="622215168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10055,14 +10159,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565891840"/>
+        <c:crossAx val="622217088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565891840"/>
+        <c:axId val="622217088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10113,7 +10217,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565584256"/>
+        <c:crossAx val="622215168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10304,7 +10408,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10481,6 +10585,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>119779016.08311573</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>116883008.32632542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10495,8 +10602,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="593340288"/>
-        <c:axId val="593338368"/>
+        <c:axId val="623033728"/>
+        <c:axId val="623032192"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10521,7 +10628,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10698,6 +10805,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10707,7 +10817,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10884,6 +10994,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10900,11 +11013,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="589926784"/>
-        <c:axId val="589928320"/>
+        <c:axId val="622778624"/>
+        <c:axId val="623030272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="589926784"/>
+        <c:axId val="622778624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10947,14 +11060,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="589928320"/>
+        <c:crossAx val="623030272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="589928320"/>
+        <c:axId val="623030272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11005,12 +11118,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="589926784"/>
+        <c:crossAx val="622778624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="593338368"/>
+        <c:axId val="623032192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11047,12 +11160,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593340288"/>
+        <c:crossAx val="623033728"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="593340288"/>
+        <c:axId val="623033728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11061,7 +11174,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="593338368"/>
+        <c:crossAx val="623032192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11240,7 +11353,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11417,6 +11530,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11426,7 +11542,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11602,6 +11718,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11645,7 +11764,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11822,6 +11941,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11831,7 +11953,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12008,6 +12130,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>154049928.53279907</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>162688850.00592482</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12050,7 +12175,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12227,6 +12352,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12236,7 +12364,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12413,6 +12541,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>70468932.197179049</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>79107853.670304805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12434,11 +12565,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="593399808"/>
-        <c:axId val="593401344"/>
+        <c:axId val="623904640"/>
+        <c:axId val="623906176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="593399808"/>
+        <c:axId val="623904640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12481,14 +12612,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593401344"/>
+        <c:crossAx val="623906176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="593401344"/>
+        <c:axId val="623906176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12539,7 +12670,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593399808"/>
+        <c:crossAx val="623904640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13253,7 +13384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -13384,28 +13515,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -15856,6 +15987,44 @@
       </c>
       <c r="L61" s="14">
         <v>1227054.0113231102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="15">
+        <v>11979550.373187648</v>
+      </c>
+      <c r="H62" s="15">
+        <v>14914540.271741569</v>
+      </c>
+      <c r="I62" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J62" s="15">
+        <v>16470742.053078819</v>
+      </c>
+      <c r="K62" s="15">
+        <v>7109407.2353513949</v>
+      </c>
+      <c r="L62" s="14">
+        <v>1556201.7813372496</v>
       </c>
     </row>
   </sheetData>
@@ -15874,7 +16043,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15912,10 +16081,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -15945,10 +16114,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15969,7 +16138,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -16049,28 +16218,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="X3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -19904,6 +20073,71 @@
       </c>
       <c r="U61" s="11">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-394977.32401696721</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-317250.86144915438</v>
+      </c>
+      <c r="G62" s="15">
+        <v>12811203.706422772</v>
+      </c>
+      <c r="H62" s="15">
+        <v>15949948.675584931</v>
+      </c>
+      <c r="I62" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J62" s="15">
+        <v>17697629.703050636</v>
+      </c>
+      <c r="K62" s="15">
+        <v>7689856.1635277644</v>
+      </c>
+      <c r="L62" s="14">
+        <v>1747681.0274657053</v>
+      </c>
+      <c r="M62" s="23">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="N62" s="23">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="O62" s="23">
+        <v>1.2263333400090535</v>
+      </c>
+      <c r="P62" s="23">
+        <v>0.9948571466264271</v>
+      </c>
+      <c r="Q62" s="23">
+        <v>0.23147619338262637</v>
+      </c>
+      <c r="R62" s="23">
+        <v>0.11985034480386848</v>
+      </c>
+      <c r="S62" s="9">
+        <v>1.7977551720580272E-3</v>
+      </c>
+      <c r="T62" s="9">
+        <v>128.75846332158676</v>
+      </c>
+      <c r="U62" s="11">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -19922,7 +20156,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19996,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -20063,28 +20297,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -22868,6 +23102,50 @@
       </c>
       <c r="N61" s="9">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-394977.32401696721</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-317250.86144915438</v>
+      </c>
+      <c r="G62" s="15">
+        <v>12761408.348849542</v>
+      </c>
+      <c r="H62" s="15">
+        <v>15887953.455168817</v>
+      </c>
+      <c r="I62" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J62" s="15">
+        <v>17567754.333578344</v>
+      </c>
+      <c r="K62" s="15">
+        <v>7604968.9543284345</v>
+      </c>
+      <c r="L62" s="14">
+        <v>1679800.8784095263</v>
+      </c>
+      <c r="M62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="N62" s="9">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -22886,7 +23164,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22921,13 +23199,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -22960,7 +23238,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -23027,28 +23305,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -25832,6 +26110,50 @@
       </c>
       <c r="N61" s="9">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-3605529.6710131839</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-2896007.7567903157</v>
+      </c>
+      <c r="G62" s="15">
+        <v>116883008.32632542</v>
+      </c>
+      <c r="H62" s="15">
+        <v>145519345.92361677</v>
+      </c>
+      <c r="I62" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J62" s="15">
+        <v>157278204.92011258</v>
+      </c>
+      <c r="K62" s="15">
+        <v>69838252.257509872</v>
+      </c>
+      <c r="L62" s="14">
+        <v>11758858.996495802</v>
+      </c>
+      <c r="M62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="N62" s="9">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -25850,7 +26172,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25885,22 +26207,22 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -25930,7 +26252,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -26005,28 +26327,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="V3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -29158,6 +29480,56 @@
       </c>
       <c r="P61" s="9">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="14">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="14">
+        <v>-2500093.7589145182</v>
+      </c>
+      <c r="H62" s="15">
+        <v>-2008107.4291880447</v>
+      </c>
+      <c r="I62" s="15">
+        <v>125034932.02531429</v>
+      </c>
+      <c r="J62" s="15">
+        <v>155668490.9677293</v>
+      </c>
+      <c r="K62" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L62" s="15">
+        <v>162688850.00592482</v>
+      </c>
+      <c r="M62" s="15">
+        <v>79107853.670304805</v>
+      </c>
+      <c r="N62" s="14">
+        <v>7020359.0381955188</v>
+      </c>
+      <c r="O62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="P62" s="9">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
